--- a/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/11_17_3_1.xlsx
+++ b/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/11_17_3_1.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40CE9C2-0936-534B-BFB7-A6BD7743FC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="9435" windowHeight="6915"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="板 1 - Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,8 +19,42 @@
     <definedName name="MethodPointer1">1785934416</definedName>
     <definedName name="MethodPointer2">594</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -289,7 +329,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -403,7 +443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -426,20 +466,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -489,29 +520,43 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="zh-CN"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -520,89 +565,6 @@
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout/>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'板 1 - Sheet1'!$Q$26:$Q$28</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.14499999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.10250000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.2499999999999995E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:axId val="183832576"/>
-        <c:axId val="97630848"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="183832576"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="b"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="97630848"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="97630848"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="183832576"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="zh-CN"/>
-  <c:chart>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:trendline>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout/>
               <c:numFmt formatCode="General" sourceLinked="0"/>
             </c:trendlineLbl>
           </c:trendline>
@@ -613,43 +575,56 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>0.04</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0.02</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.05</c:v>
+                  <c:v>1E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'板 1 - Sheet1'!$Q$26:$Q$29</c:f>
+              <c:f>'板 1 - Sheet1'!$R$26:$R$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.14499999999999999</c:v>
+                  <c:v>9.2999999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.10250000000000001</c:v>
+                  <c:v>5.050000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.2499999999999995E-2</c:v>
+                  <c:v>2.0499999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.7500000000000002E-2</c:v>
+                  <c:v>5.5000000000000049E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-44C9-E24A-940D-064CA53779BC}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="184436608"/>
         <c:axId val="184421760"/>
       </c:scatterChart>
@@ -658,8 +633,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="184421760"/>
         <c:crosses val="autoZero"/>
@@ -670,21 +648,26 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="184436608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -695,36 +678,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="图表 4"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
@@ -740,7 +693,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="图表 5"/>
+        <xdr:cNvPr id="6" name="图表 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -749,7 +708,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -759,7 +718,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -801,7 +760,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -833,9 +792,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -867,6 +844,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1042,15 +1037,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:Q32"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:AC47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +1053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="14">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1066,12 +1061,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="14">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="14">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1079,7 +1074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="14">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1087,7 +1082,7 @@
         <v>45613</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="14">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1095,7 +1090,7 @@
         <v>0.64858796296296295</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="14">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,7 +1098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="14">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1111,7 +1106,7 @@
         <v>19012425</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="14">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1119,13 +1114,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="14">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1133,12 +1128,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="14">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1146,62 +1141,82 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:18" ht="14">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="Q17">
-        <f>(E25+F25)/2</f>
+        <f t="shared" ref="Q17:Q24" si="0">(E25+F25)/2</f>
         <v>6.4500000000000002E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17">
+        <f t="shared" ref="R17:R31" si="1">Q17-0.052</f>
+        <v>1.2500000000000004E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="14">
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P18">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="Q18">
-        <f>(E26+F26)/2</f>
+        <f t="shared" si="0"/>
         <v>0.30399999999999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18">
+        <f t="shared" si="1"/>
+        <v>0.252</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="14">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
       <c r="P19">
-        <v>9</v>
+        <v>0.18</v>
       </c>
       <c r="Q19">
-        <f>(E27+F27)/2</f>
+        <f t="shared" si="0"/>
         <v>0.24349999999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19">
+        <f t="shared" si="1"/>
+        <v>0.1915</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="P20">
-        <v>8</v>
+        <v>0.16</v>
       </c>
       <c r="Q20">
-        <f>(E28+F28)/2</f>
+        <f t="shared" si="0"/>
         <v>0.5595</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20">
+        <f t="shared" si="1"/>
+        <v>0.50749999999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="14">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="5"/>
       <c r="P21">
-        <v>7</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Q21">
-        <f>(E29+F29)/2</f>
+        <f t="shared" si="0"/>
         <v>0.50149999999999995</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21">
+        <f t="shared" si="1"/>
+        <v>0.44949999999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="14">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -1209,23 +1224,31 @@
         <v>22.7</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>0.12</v>
       </c>
       <c r="Q22">
-        <f>(E30+F30)/2</f>
+        <f t="shared" si="0"/>
         <v>0.22399999999999998</v>
       </c>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="R22">
+        <f t="shared" si="1"/>
+        <v>0.17199999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="P23">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="Q23">
-        <f>(E31+F31)/2</f>
+        <f t="shared" si="0"/>
         <v>0.254</v>
       </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R23">
+        <f t="shared" si="1"/>
+        <v>0.20200000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="B24" s="6"/>
       <c r="C24" s="7">
         <v>1</v>
@@ -1263,15 +1286,19 @@
       <c r="N24" s="7">
         <v>12</v>
       </c>
-      <c r="P24" s="20">
-        <v>4</v>
+      <c r="P24">
+        <v>0.08</v>
       </c>
       <c r="Q24">
-        <f>(E32+F32)/2</f>
+        <f t="shared" si="0"/>
         <v>8.5999999999999993E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="R24">
+        <f t="shared" si="1"/>
+        <v>3.3999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="14">
       <c r="B25" s="7" t="s">
         <v>25</v>
       </c>
@@ -1314,15 +1341,19 @@
       <c r="O25" s="10">
         <v>560</v>
       </c>
-      <c r="P25" s="19">
-        <v>3</v>
+      <c r="P25">
+        <v>0.06</v>
       </c>
       <c r="Q25">
-        <f>(C25+D25)/2</f>
+        <f t="shared" ref="Q25:Q32" si="2">(C25+D25)/2</f>
         <v>0.09</v>
       </c>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="R25">
+        <f t="shared" si="1"/>
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="14">
       <c r="B26" s="7" t="s">
         <v>26</v>
       </c>
@@ -1365,15 +1396,19 @@
       <c r="O26" s="10">
         <v>560</v>
       </c>
-      <c r="P26" s="19">
-        <v>2</v>
+      <c r="P26">
+        <v>0.04</v>
       </c>
       <c r="Q26">
-        <f>(C26+D26)/2</f>
+        <f t="shared" si="2"/>
         <v>0.14499999999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="R26">
+        <f t="shared" si="1"/>
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="14">
       <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1416,15 +1451,19 @@
       <c r="O27" s="10">
         <v>560</v>
       </c>
-      <c r="P27" s="19">
-        <v>1</v>
+      <c r="P27">
+        <v>0.02</v>
       </c>
       <c r="Q27">
-        <f>(C27+D27)/2</f>
+        <f t="shared" si="2"/>
         <v>0.10250000000000001</v>
       </c>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="R27">
+        <f t="shared" si="1"/>
+        <v>5.050000000000001E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="14">
       <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1467,15 +1506,19 @@
       <c r="O28" s="10">
         <v>560</v>
       </c>
-      <c r="P28" s="19">
-        <v>0.5</v>
+      <c r="P28">
+        <v>0.01</v>
       </c>
       <c r="Q28">
-        <f>(C28+D28)/2</f>
+        <f t="shared" si="2"/>
         <v>7.2499999999999995E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="R28">
+        <f t="shared" si="1"/>
+        <v>2.0499999999999997E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="14">
       <c r="B29" s="7" t="s">
         <v>29</v>
       </c>
@@ -1518,15 +1561,19 @@
       <c r="O29" s="10">
         <v>560</v>
       </c>
-      <c r="P29" s="19">
-        <v>0.05</v>
+      <c r="P29">
+        <v>1E-3</v>
       </c>
       <c r="Q29">
-        <f>(C29+D29)/2</f>
+        <f t="shared" si="2"/>
         <v>5.7500000000000002E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="R29">
+        <f t="shared" si="1"/>
+        <v>5.5000000000000049E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="14">
       <c r="B30" s="7" t="s">
         <v>30</v>
       </c>
@@ -1569,15 +1616,19 @@
       <c r="O30" s="10">
         <v>560</v>
       </c>
-      <c r="P30" s="19">
-        <v>5.0000000000000001E-3</v>
+      <c r="P30">
+        <v>1E-4</v>
       </c>
       <c r="Q30">
-        <f>(C30+D30)/2</f>
+        <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="R30">
+        <f t="shared" si="1"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="14">
       <c r="B31" s="7" t="s">
         <v>31</v>
       </c>
@@ -1620,15 +1671,19 @@
       <c r="O31" s="10">
         <v>560</v>
       </c>
-      <c r="P31" s="19">
-        <v>5.0000000000000001E-4</v>
+      <c r="P31">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Q31">
-        <f>(C31+D31)/2</f>
+        <f t="shared" si="2"/>
         <v>5.1999999999999998E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="R31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="14">
       <c r="B32" s="7" t="s">
         <v>32</v>
       </c>
@@ -1671,15 +1726,536 @@
       <c r="O32" s="10">
         <v>560</v>
       </c>
-      <c r="P32" s="19">
+      <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32">
-        <f>(C32+D32)/2</f>
+        <f t="shared" si="2"/>
         <v>5.1999999999999998E-2</v>
       </c>
+      <c r="R32">
+        <f>Q32-0.052</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:29">
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39">
+        <v>6</v>
+      </c>
+      <c r="I39">
+        <v>7</v>
+      </c>
+      <c r="J39">
+        <v>8</v>
+      </c>
+      <c r="M39">
+        <v>8</v>
+      </c>
+      <c r="N39">
+        <v>7</v>
+      </c>
+      <c r="O39">
+        <v>6</v>
+      </c>
+      <c r="P39">
+        <v>5</v>
+      </c>
+      <c r="Q39">
+        <v>4</v>
+      </c>
+      <c r="R39">
+        <v>3</v>
+      </c>
+      <c r="S39">
+        <v>2</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="3:29">
+      <c r="C40" cm="1">
+        <f t="array" ref="C40:J43">TRANSPOSE(C25:F32)</f>
+        <v>0.104</v>
+      </c>
+      <c r="D40">
+        <v>0.18</v>
+      </c>
+      <c r="E40">
+        <v>0.106</v>
+      </c>
+      <c r="F40">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="G40">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="H40">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="I40">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="J40">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="M40">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="N40">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="O40">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="P40">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="Q40">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="R40">
+        <v>0.106</v>
+      </c>
+      <c r="S40">
+        <v>0.18</v>
+      </c>
+      <c r="T40">
+        <v>0.104</v>
+      </c>
+      <c r="V40">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="W40">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="X40">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="Y40">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="Z40">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="AA40">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="AB40">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="AC40">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="3:29">
+      <c r="C41">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="D41">
+        <v>0.11</v>
+      </c>
+      <c r="E41">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="F41">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="G41">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="H41">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="I41">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="J41">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="M41">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="N41">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="O41">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="P41">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="Q41">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="R41">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="S41">
+        <v>0.11</v>
+      </c>
+      <c r="T41">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="V41">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="W41">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="X41">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="Y41">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="Z41">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="AA41">
+        <v>6.3E-2</v>
+      </c>
+      <c r="AB41">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="AC41">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="3:29">
+      <c r="C42">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="D42">
+        <v>0.311</v>
+      </c>
+      <c r="E42">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="F42">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="G42">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="H42">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I42">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="J42">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="M42">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="N42">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="O42">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="P42">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="Q42">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="R42">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="S42">
+        <v>0.311</v>
+      </c>
+      <c r="T42">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="V42">
+        <f>(V40+V41)/2</f>
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="W42">
+        <f>(W40+W41)/2</f>
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="X42">
+        <f>(X40+X41)/2</f>
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="Y42">
+        <f>(Y40+Y41)/2</f>
+        <v>5.5500000000000001E-2</v>
+      </c>
+      <c r="Z42">
+        <f>(Z40+Z41)/2</f>
+        <v>5.3499999999999999E-2</v>
+      </c>
+      <c r="AA42">
+        <f>(AA40+AA41)/2</f>
+        <v>5.7499999999999996E-2</v>
+      </c>
+      <c r="AB42">
+        <f>(AB40+AB41)/2</f>
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="AC42">
+        <f>(AC40+AC41)/2</f>
+        <v>4.65E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="3:29">
+      <c r="C43">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="D43">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="E43">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="F43">
+        <v>0.437</v>
+      </c>
+      <c r="G43">
+        <v>0.82599999999999996</v>
+      </c>
+      <c r="H43">
+        <v>0.21</v>
+      </c>
+      <c r="I43">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="J43">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M43">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N43">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="O43">
+        <v>0.21</v>
+      </c>
+      <c r="P43">
+        <v>0.82599999999999996</v>
+      </c>
+      <c r="Q43">
+        <v>0.437</v>
+      </c>
+      <c r="R43">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="S43">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="T43">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="V43">
+        <f>ABS(V40-V41)</f>
+        <v>2.4000000000000007E-2</v>
+      </c>
+      <c r="W43">
+        <f>ABS(W40-W41)</f>
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <f>ABS(X40-X41)</f>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="Y43">
+        <f>ABS(Y40-Y41)</f>
+        <v>3.0000000000000027E-3</v>
+      </c>
+      <c r="Z43">
+        <f>ABS(Z40-Z41)</f>
+        <v>1.0000000000000009E-3</v>
+      </c>
+      <c r="AA43">
+        <f>ABS(AA40-AA41)</f>
+        <v>1.1000000000000003E-2</v>
+      </c>
+      <c r="AB43">
+        <f>ABS(AB40-AB41)</f>
+        <v>4.0000000000000036E-3</v>
+      </c>
+      <c r="AC43">
+        <f>ABS(AC40-AC41)</f>
+        <v>3.0000000000000027E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="3:29">
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+      <c r="H45">
+        <v>6</v>
+      </c>
+      <c r="I45">
+        <v>7</v>
+      </c>
+      <c r="J45">
+        <v>8</v>
+      </c>
+      <c r="M45">
+        <v>8</v>
+      </c>
+      <c r="N45">
+        <v>7</v>
+      </c>
+      <c r="O45">
+        <v>6</v>
+      </c>
+      <c r="P45">
+        <v>5</v>
+      </c>
+      <c r="Q45">
+        <v>4</v>
+      </c>
+      <c r="R45">
+        <v>3</v>
+      </c>
+      <c r="S45">
+        <v>2</v>
+      </c>
+      <c r="T45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="3:29">
+      <c r="C46" cm="1">
+        <f t="array" ref="C46:J47">TRANSPOSE(H25:I32)</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D46">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="E46">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="F46">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="G46">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="H46">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="I46">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="J46">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="M46">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="N46">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="O46">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="P46">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="Q46">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="R46">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="S46">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="T46">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="3:29">
+      <c r="C47">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="D47">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="E47">
+        <v>6.3E-2</v>
+      </c>
+      <c r="F47">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G47">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="H47">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I47">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="J47">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="M47">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="N47">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="O47">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="P47">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="Q47">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="R47">
+        <v>6.3E-2</v>
+      </c>
+      <c r="S47">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="T47">
+        <v>4.8000000000000001E-2</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="M45:T47">
+    <sortCondition descending="1" ref="M45:T45"/>
+  </sortState>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
